--- a/curation/draft/package16/R16_BC_SDTM_VS.xlsx
+++ b/curation/draft/package16/R16_BC_SDTM_VS.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_github\cdisc-org\COSMoS\curation\draft\package16\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A77AF48B-3000-40F3-9857-069F6335C8B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14BAE2D2-3C50-4524-80B4-052583893B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BC_VS" sheetId="1" r:id="rId1"/>
     <sheet name="SDTM_VS" sheetId="2" r:id="rId2"/>
+    <sheet name="SDTM_VS_Updates" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BC_VS!$A$1:$Q$189</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SDTM_VS!$A$1:$AF$473</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12000" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12196" uniqueCount="556">
   <si>
     <t>package_date</t>
   </si>
@@ -1670,13 +1671,52 @@
   </si>
   <si>
     <t>R16</t>
+  </si>
+  <si>
+    <t>C16358</t>
+  </si>
+  <si>
+    <t>BMI</t>
+  </si>
+  <si>
+    <t>Body Mass Index</t>
+  </si>
+  <si>
+    <t>8.3</t>
+  </si>
+  <si>
+    <t>Derived</t>
+  </si>
+  <si>
+    <t>Sponsor</t>
+  </si>
+  <si>
+    <t>C42575</t>
+  </si>
+  <si>
+    <t>C71620</t>
+  </si>
+  <si>
+    <t>UNIT</t>
+  </si>
+  <si>
+    <t>UNIT_BMI</t>
+  </si>
+  <si>
+    <t>kg/m2;psi</t>
+  </si>
+  <si>
+    <t>Add significant_digits</t>
+  </si>
+  <si>
+    <t>change_history</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1725,6 +1765,12 @@
       <color rgb="FF112277"/>
       <name val="Albany AMT"/>
     </font>
+    <font>
+      <u/>
+      <sz val="9.5"/>
+      <color rgb="FF0000FF"/>
+      <name val="Albany AMT"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1758,7 +1804,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1835,11 +1881,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD3D3D3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1888,6 +1949,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -41286,4 +41353,782 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BCD3AC8-5DAA-4F2C-90C8-073A074BB7D2}">
+  <dimension ref="A1:AG9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" style="10" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" style="10" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" style="10" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="10"/>
+    <col min="6" max="6" width="13.7109375" style="10" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" style="10" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" style="10" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" style="10" customWidth="1"/>
+    <col min="10" max="12" width="9.140625" style="10"/>
+    <col min="13" max="13" width="19.42578125" style="10" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="10" customWidth="1"/>
+    <col min="15" max="15" width="13.5703125" style="10" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" style="10"/>
+    <col min="17" max="17" width="20.5703125" style="10" customWidth="1"/>
+    <col min="18" max="18" width="9.140625" style="10"/>
+    <col min="19" max="19" width="11.7109375" style="10" customWidth="1"/>
+    <col min="20" max="20" width="28.5703125" style="10" customWidth="1"/>
+    <col min="21" max="21" width="22.5703125" style="10" customWidth="1"/>
+    <col min="22" max="22" width="16.28515625" style="10" customWidth="1"/>
+    <col min="23" max="23" width="12.42578125" style="10" customWidth="1"/>
+    <col min="24" max="25" width="9.140625" style="10"/>
+    <col min="26" max="26" width="8.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9" style="10" bestFit="1" customWidth="1"/>
+    <col min="28" max="32" width="9.140625" style="10"/>
+    <col min="33" max="33" width="21.5703125" style="10" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:33" s="9" customFormat="1" ht="39" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="V1" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="W1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="X1" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="Y1" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="Z1" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="AA1" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="AB1" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="AC1" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="AD1" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="AE1" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="AF1" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="AG1" s="8" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
+        <v>542</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>437</v>
+      </c>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17" t="s">
+        <v>438</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>439</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>544</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>545</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>440</v>
+      </c>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>442</v>
+      </c>
+      <c r="M2" s="17" t="s">
+        <v>440</v>
+      </c>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17" t="s">
+        <v>543</v>
+      </c>
+      <c r="Q2" s="17" t="s">
+        <v>544</v>
+      </c>
+      <c r="R2" s="17" t="s">
+        <v>443</v>
+      </c>
+      <c r="S2" s="17" t="s">
+        <v>440</v>
+      </c>
+      <c r="T2" s="17" t="s">
+        <v>444</v>
+      </c>
+      <c r="U2" s="17" t="s">
+        <v>445</v>
+      </c>
+      <c r="V2" s="17" t="s">
+        <v>446</v>
+      </c>
+      <c r="W2" s="17"/>
+      <c r="X2" s="17"/>
+      <c r="Y2" s="17"/>
+      <c r="Z2" s="17"/>
+      <c r="AA2" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="AB2" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="AC2" s="17"/>
+      <c r="AD2" s="17"/>
+      <c r="AE2" s="17" t="s">
+        <v>448</v>
+      </c>
+      <c r="AF2" s="17"/>
+      <c r="AG2" s="17"/>
+    </row>
+    <row r="3" spans="1:33" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
+        <v>542</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>437</v>
+      </c>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17" t="s">
+        <v>438</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>439</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>544</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>545</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>446</v>
+      </c>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>449</v>
+      </c>
+      <c r="M3" s="17" t="s">
+        <v>446</v>
+      </c>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17" t="s">
+        <v>543</v>
+      </c>
+      <c r="Q3" s="17" t="s">
+        <v>545</v>
+      </c>
+      <c r="R3" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="S3" s="17" t="s">
+        <v>446</v>
+      </c>
+      <c r="T3" s="17" t="s">
+        <v>451</v>
+      </c>
+      <c r="U3" s="17" t="s">
+        <v>452</v>
+      </c>
+      <c r="V3" s="17" t="s">
+        <v>440</v>
+      </c>
+      <c r="W3" s="17"/>
+      <c r="X3" s="17"/>
+      <c r="Y3" s="17"/>
+      <c r="Z3" s="17"/>
+      <c r="AA3" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="AB3" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="AC3" s="17"/>
+      <c r="AD3" s="17"/>
+      <c r="AE3" s="17"/>
+      <c r="AF3" s="17"/>
+      <c r="AG3" s="17"/>
+    </row>
+    <row r="4" spans="1:33" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>542</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>437</v>
+      </c>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17" t="s">
+        <v>438</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>439</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>544</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>545</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>453</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="S4" s="17" t="s">
+        <v>453</v>
+      </c>
+      <c r="T4" s="17" t="s">
+        <v>454</v>
+      </c>
+      <c r="U4" s="17" t="s">
+        <v>455</v>
+      </c>
+      <c r="V4" s="17" t="s">
+        <v>440</v>
+      </c>
+      <c r="W4" s="17" t="s">
+        <v>534</v>
+      </c>
+      <c r="X4" s="17">
+        <v>8</v>
+      </c>
+      <c r="Y4" s="17" t="s">
+        <v>546</v>
+      </c>
+      <c r="Z4" s="17">
+        <v>3</v>
+      </c>
+      <c r="AA4" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="AB4" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="AC4" s="17" t="s">
+        <v>547</v>
+      </c>
+      <c r="AD4" s="17" t="s">
+        <v>548</v>
+      </c>
+      <c r="AE4" s="17"/>
+      <c r="AF4" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="AG4" s="17" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>542</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>437</v>
+      </c>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17" t="s">
+        <v>438</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>439</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>544</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>545</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>458</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>549</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="L5" s="18" t="s">
+        <v>550</v>
+      </c>
+      <c r="M5" s="17" t="s">
+        <v>551</v>
+      </c>
+      <c r="N5" s="17" t="s">
+        <v>552</v>
+      </c>
+      <c r="O5" s="17" t="s">
+        <v>553</v>
+      </c>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="S5" s="17" t="s">
+        <v>458</v>
+      </c>
+      <c r="T5" s="17" t="s">
+        <v>461</v>
+      </c>
+      <c r="U5" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="V5" s="17" t="s">
+        <v>453</v>
+      </c>
+      <c r="W5" s="17"/>
+      <c r="X5" s="17"/>
+      <c r="Y5" s="17"/>
+      <c r="Z5" s="17"/>
+      <c r="AA5" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="AB5" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="AC5" s="17"/>
+      <c r="AD5" s="17"/>
+      <c r="AE5" s="17"/>
+      <c r="AF5" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="AG5" s="17"/>
+    </row>
+    <row r="6" spans="1:33" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
+        <v>542</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>437</v>
+      </c>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17" t="s">
+        <v>438</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>439</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>544</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>545</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>463</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="S6" s="17" t="s">
+        <v>463</v>
+      </c>
+      <c r="T6" s="17" t="s">
+        <v>454</v>
+      </c>
+      <c r="U6" s="17" t="s">
+        <v>455</v>
+      </c>
+      <c r="V6" s="17" t="s">
+        <v>440</v>
+      </c>
+      <c r="W6" s="17" t="s">
+        <v>534</v>
+      </c>
+      <c r="X6" s="17">
+        <v>8</v>
+      </c>
+      <c r="Y6" s="17" t="s">
+        <v>546</v>
+      </c>
+      <c r="Z6" s="17">
+        <v>3</v>
+      </c>
+      <c r="AA6" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="AB6" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="AC6" s="17"/>
+      <c r="AD6" s="17"/>
+      <c r="AE6" s="17"/>
+      <c r="AF6" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="AG6" s="17"/>
+    </row>
+    <row r="7" spans="1:33" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
+        <v>542</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>437</v>
+      </c>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17" t="s">
+        <v>438</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>439</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>544</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>545</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>464</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="S7" s="17" t="s">
+        <v>464</v>
+      </c>
+      <c r="T7" s="17" t="s">
+        <v>454</v>
+      </c>
+      <c r="U7" s="17" t="s">
+        <v>455</v>
+      </c>
+      <c r="V7" s="17" t="s">
+        <v>440</v>
+      </c>
+      <c r="W7" s="17" t="s">
+        <v>534</v>
+      </c>
+      <c r="X7" s="17">
+        <v>8</v>
+      </c>
+      <c r="Y7" s="17" t="s">
+        <v>546</v>
+      </c>
+      <c r="Z7" s="17">
+        <v>3</v>
+      </c>
+      <c r="AA7" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="AB7" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="AC7" s="17"/>
+      <c r="AD7" s="17"/>
+      <c r="AE7" s="17"/>
+      <c r="AF7" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="AG7" s="17"/>
+    </row>
+    <row r="8" spans="1:33" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
+        <v>542</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>437</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17" t="s">
+        <v>438</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>439</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>544</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>545</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>465</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>549</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="L8" s="18" t="s">
+        <v>459</v>
+      </c>
+      <c r="M8" s="17" t="s">
+        <v>460</v>
+      </c>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="S8" s="17" t="s">
+        <v>465</v>
+      </c>
+      <c r="T8" s="17" t="s">
+        <v>461</v>
+      </c>
+      <c r="U8" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="V8" s="17" t="s">
+        <v>464</v>
+      </c>
+      <c r="W8" s="17"/>
+      <c r="X8" s="17"/>
+      <c r="Y8" s="17"/>
+      <c r="Z8" s="17"/>
+      <c r="AA8" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="AB8" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="AC8" s="17"/>
+      <c r="AD8" s="17"/>
+      <c r="AE8" s="17"/>
+      <c r="AF8" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="AG8" s="17"/>
+    </row>
+    <row r="9" spans="1:33" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
+        <v>542</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>437</v>
+      </c>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17" t="s">
+        <v>438</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>439</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>544</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>545</v>
+      </c>
+      <c r="I9" s="17" t="s">
+        <v>466</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17" t="s">
+        <v>467</v>
+      </c>
+      <c r="S9" s="17" t="s">
+        <v>466</v>
+      </c>
+      <c r="T9" s="17" t="s">
+        <v>468</v>
+      </c>
+      <c r="U9" s="17" t="s">
+        <v>469</v>
+      </c>
+      <c r="V9" s="17" t="s">
+        <v>440</v>
+      </c>
+      <c r="W9" s="17"/>
+      <c r="X9" s="17"/>
+      <c r="Y9" s="17"/>
+      <c r="Z9" s="17"/>
+      <c r="AA9" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="AB9" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="AC9" s="17"/>
+      <c r="AD9" s="17"/>
+      <c r="AE9" s="17"/>
+      <c r="AF9" s="17"/>
+      <c r="AG9" s="17"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{F3C530FC-8509-46BD-A983-6E4750FF2D59}"/>
+    <hyperlink ref="L2" r:id="rId2" xr:uid="{4DF55782-6582-439B-BA4F-9688C5937749}"/>
+    <hyperlink ref="B3" r:id="rId3" xr:uid="{8FC06D43-7291-438B-822C-4BF0C9560A95}"/>
+    <hyperlink ref="L3" r:id="rId4" xr:uid="{7DF1A583-B835-482E-8232-0894CE6B249B}"/>
+    <hyperlink ref="B4" r:id="rId5" xr:uid="{6C05062F-2CDE-4B59-96D2-F6959B581997}"/>
+    <hyperlink ref="J4" r:id="rId6" xr:uid="{804C8673-1022-44C7-AA7C-1580A915AF94}"/>
+    <hyperlink ref="B5" r:id="rId7" xr:uid="{2D857597-0713-40B0-B418-4944E8CAE798}"/>
+    <hyperlink ref="J5" r:id="rId8" xr:uid="{6201403D-0227-4D8B-8203-465B8D539045}"/>
+    <hyperlink ref="L5" r:id="rId9" xr:uid="{262A2965-5746-4E49-9CA1-CE00CDF42639}"/>
+    <hyperlink ref="B6" r:id="rId10" xr:uid="{BD1DFB6E-99FA-4997-8364-9FB7F1C4D40F}"/>
+    <hyperlink ref="J6" r:id="rId11" xr:uid="{A603D1E5-DAA3-41BC-9B46-616634F8E5D4}"/>
+    <hyperlink ref="B7" r:id="rId12" xr:uid="{4B4FC8A0-4EB5-40F0-BFBB-94EFF86A871A}"/>
+    <hyperlink ref="J7" r:id="rId13" xr:uid="{9279DA5F-6728-45BF-8E8C-F0C851FB61CF}"/>
+    <hyperlink ref="B8" r:id="rId14" xr:uid="{BF326178-85E1-4121-A867-AD7894EB5F09}"/>
+    <hyperlink ref="J8" r:id="rId15" xr:uid="{B08409A2-4EB5-4C09-B024-28A12D2BBB85}"/>
+    <hyperlink ref="L8" r:id="rId16" xr:uid="{012EB720-1445-4DE5-B1EE-EB89E879B303}"/>
+    <hyperlink ref="B9" r:id="rId17" xr:uid="{C51115CD-C920-48D8-835A-F9B8F3E00D53}"/>
+    <hyperlink ref="J9" r:id="rId18" xr:uid="{6E33F70D-4D8E-4864-80BC-1F9376211F90}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>